--- a/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="查询子句" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="对应sql语句列表" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>where</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,7 +190,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>跑事务</t>
+    <t>暂时不考虑测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只跑该工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖：in、not in、exists、not exists、比较符、any、all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖：自连接、左外连接、右外连接、自然连接、内连接</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -198,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +233,28 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -243,9 +281,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,7 +584,7 @@
   <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.5" customWidth="1"/>
+    <col min="1" max="1" width="25.375" customWidth="1"/>
     <col min="2" max="2" width="17.75" customWidth="1"/>
     <col min="3" max="3" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="17.625" customWidth="1"/>
@@ -709,18 +750,33 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="B13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1">
@@ -728,7 +784,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="20.100000000000001" customHeight="1"/>

--- a/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
@@ -16,97 +16,193 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
+  <si>
+    <t>select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>from</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定单列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定多列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>order by</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排序方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>between and</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>like</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算字段、拼接字段、列别名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本处理函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期和时间处理函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值处理函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集不同值:distinct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合聚集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group by</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>having</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表别名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit/offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regexp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>联接查询(外联接、内联接)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列名1=列名2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tpcds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tpcc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时不考虑测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只跑该工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖：in、not in、exists、not exists、比较符、any、all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖：自连接、左外连接、右外连接、自然连接、内连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>where</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>select</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>列名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>from</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定单列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指定多列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>order by</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>列位置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排序方向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作符：=、&lt;&gt;、！=、&lt;、&lt;=、&gt;、&gt;=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>between and</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>is null</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>and、or</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in</t>
+    <t>and</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>or</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -114,99 +210,149 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>like</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算字段、拼接字段、列别名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文本处理函数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期和时间处理函数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数值处理函数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集函数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集不同值:distinct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合聚集</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>group by</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>having</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表别名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>limit/offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>子查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>regexp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>联接查询(外联接、内联接)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>列名1=列名2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tpcds</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tpcc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暂时不考虑测试</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只跑该工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖：in、not in、exists、not exists、比较符、any、all</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖：自连接、左外连接、右外连接、自然连接、内连接</t>
+    <t>a字段为索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a、b字段均为索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a like x and b regex x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a is null and b in x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a =x and  a=b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a!=x and b&lt;&gt;x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a&gt;x and b&lt;=x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wehre a&gt;=x and b&lt;x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a&gt;x and a&lt;=x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wehre a&gt;=x and a&lt;x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a!=x and a&lt;&gt;x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a =x and  a=b(覆盖b字段为索引)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a字段为索引或者b字段为索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a&gt;x or a&lt;=x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wehre a&gt;=x or a&lt;x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a!=x or a&lt;&gt;x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a =x or  a=b(覆盖b字段为索引)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>where a&gt;x or b&lt;=x</t>
+  </si>
+  <si>
+    <t>wehre a&gt;=x or b&lt;x</t>
+  </si>
+  <si>
+    <t>where a!=x or b&lt;&gt;x</t>
+  </si>
+  <si>
+    <t>where a =x or  a=b</t>
+  </si>
+  <si>
+    <t>where a is null or b in x</t>
+  </si>
+  <si>
+    <t>where a like x or b regex x</t>
+  </si>
+  <si>
+    <t>COALESCE()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作符：=、&lt;&gt;、！=、&lt;、&lt;=、&gt;、&gt;=、&lt;=&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GREATEST()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INTERVAL()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IS NOT NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IS NOT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LEAST()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT BETWEEN ... AND …</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT IN()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT LIKE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRCMP()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&amp;&amp;、！、||</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>and、or、not、xor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ISNULL()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -581,14 +727,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" customWidth="1"/>
     <col min="2" max="2" width="17.75" customWidth="1"/>
     <col min="3" max="3" width="17.875" customWidth="1"/>
     <col min="4" max="4" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="18.625" customWidth="1"/>
+    <col min="6" max="6" width="45.75" customWidth="1"/>
     <col min="7" max="7" width="11.5" customWidth="1"/>
     <col min="8" max="8" width="7.5" customWidth="1"/>
     <col min="9" max="9" width="8.625" customWidth="1"/>
@@ -600,198 +746,243 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
         <v>11</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="B12" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" ht="20.100000000000001" customHeight="1"/>
-    <row r="18" ht="20.100000000000001" customHeight="1"/>
-    <row r="19" ht="20.100000000000001" customHeight="1"/>
-    <row r="20" ht="20.100000000000001" customHeight="1"/>
-    <row r="21" ht="20.100000000000001" customHeight="1"/>
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" ht="20.100000000000001" customHeight="1">
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" ht="20.100000000000001" customHeight="1">
+      <c r="F18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" ht="20.100000000000001" customHeight="1">
+      <c r="F19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" ht="20.100000000000001" customHeight="1">
+      <c r="F20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" ht="20.100000000000001" customHeight="1">
+      <c r="F21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6">
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6">
+      <c r="F23" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -801,9 +992,158 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.75" customWidth="1"/>
+    <col min="2" max="2" width="37.625" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="87">
   <si>
     <t>select</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -353,6 +353,10 @@
   </si>
   <si>
     <t>ISNULL()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更详细的参考mysql官网文档</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -727,12 +731,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.375" customWidth="1"/>
     <col min="2" max="2" width="17.75" customWidth="1"/>
-    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="26.125" customWidth="1"/>
     <col min="4" max="4" width="17.625" customWidth="1"/>
     <col min="6" max="6" width="45.75" customWidth="1"/>
     <col min="7" max="7" width="11.5" customWidth="1"/>
@@ -948,39 +952,44 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="6:6" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="F17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="6:6" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="F18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="6:6" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="F19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="6:6" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="F20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="6:6" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="3:6" ht="20.100000000000001" customHeight="1">
       <c r="F21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="6:6">
+    <row r="22" spans="3:6">
       <c r="F22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="6:6">
+    <row r="23" spans="3:6">
       <c r="F23" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/关键字列表.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="查询子句" sheetId="1" r:id="rId1"/>
     <sheet name="对应sql语句列表" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="函数和操作符" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="125">
   <si>
     <t>select</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -357,6 +357,158 @@
   </si>
   <si>
     <t>更详细的参考mysql官网文档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符串函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASCII()、BIN()、BIT_LENGTH()、CHAR_LENGTH()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FROM_BASE64()、HEX()、INSERT()、INSTR()、LCASE()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LEFT()、LENGTH()、LOAD_FILE()、LOCATE()、LOWER()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LPAD()、LTRIM()、REPEAT()、REPLACE()、REVERSE()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RIGTH()、RPAD()、RTRIM()、SOUNDEX()、SPACE()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRCMP()、SUBSTR()、SUBSTRING_INDEX()、SUBSTRING()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO_BASE64()、TRIM()、UCASE()、UNHEX()、UPPER()、WEIGHT_STRING()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>函数和操作符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符操作符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIKE、NOT LIKE、REGEXP、NOT REGEXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>、RELIKE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABS()、ACOS()、ASIN()、ATAN2()、ATAN()、CEIL()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHAR()、CHARACTER_LENGTH()、CONCAT_WS()、CONCAT()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ELT()、EXPORT_SET()、FIELD()、FIND_IN_SET()、FORMAT()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CEILING()、CONV()、COS()、COT()、CRC32()、DEGREES()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXP()、FLOOR()、LN()、LOG10()、LOG2()、LOG()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOD()、PI()、POW()、POWER()、RADIANS()、RAND()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROUND()、SIGN()、SIN()、SORT()、TAN()、TRUNCATE()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学操作符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIV、MOD、/、-、%、+、*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间函数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDDATE()、ADDTIME()、CONVERT_TZ()、CURDATE()、CURRENT_DATE()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CURRENT_TIME()、CURRENT_TIMESTAMP()、CURTIME()、DATE_ADD()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE_FORMAT()、DATE_SUB()、DATE()、DATEDIFF()、DAY()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAYNAME()、DAYOFMONTH()、DAYOFWEEK()、DAYOFYEAR()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXTRACT()、FROM_DAYS()、FROM_UNIXTIME()、GET_FROMAT()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOUR()、LAST_DAY、LOCALTIME()、LOCALTIMESTAMP()、MAKEdATE()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAKETIME()、MICROSECOND()、MINUTE()、MONTH()、MONTHNAME()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOW()、PERIOD_ADD()、PERIOD_DIFF()、QUARTER()、SEC_TO_TIME()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SECOND()、STR_TO_DATE()、SUBDATE()、SUBTIME()、SYSDATE()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIME_FORMAT()、TIME_TO_SEC()、TIME()、TIMEDIFF()、TIMESTAMP()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIMESTAMPADD()、TIMESTAMPDIFF()、TO_DAYS()、TO_SECONDS()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIX_TIMESTAMP()、UTC_DATE()、UTC_TIME()、UTC_TIMESTAMP()、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEK()、WEEKDAY()、WEEKOFYEAR()、YEAR()、YEARWEEK()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制流函数和操作符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASE、IF()、IFNULLL()、NULLIF()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1160,10 +1312,188 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="C30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="C32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="C33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="C34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="C35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="C36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="C39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>